--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/mar-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/mar-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>16329.07</v>
+        <v>17036</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>619.4</v>
+        <v>646.22</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10661.92</v>
+        <v>11123.51</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>36312.53</v>
+        <v>37884.62</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1035505.11</v>
+        <v>1064847.91</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>696818.85</v>
+        <v>716564.4</v>
       </c>
     </row>
     <row r="8">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5386172.79</v>
+        <v>5472729.65</v>
       </c>
     </row>
     <row r="9">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>316975.97</v>
+        <v>317672.53</v>
       </c>
     </row>
     <row r="10">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1248.69</v>
+        <v>1240.09</v>
       </c>
     </row>
     <row r="11">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>296228.46</v>
+        <v>296262.25</v>
       </c>
     </row>
     <row r="12">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11910.61</v>
+        <v>11922.85</v>
       </c>
     </row>
     <row r="13">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7828.35</v>
+        <v>7784.67</v>
       </c>
     </row>
     <row r="14">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>75017.64999999999</v>
+        <v>74599.08</v>
       </c>
     </row>
     <row r="15">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10709.95</v>
+        <v>10643.09</v>
       </c>
     </row>
     <row r="16">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10181.65</v>
+        <v>10139.47</v>
       </c>
     </row>
     <row r="17">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>727892.1</v>
+        <v>717480.3100000001</v>
       </c>
     </row>
     <row r="18">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>192.11</v>
+        <v>189.36</v>
       </c>
     </row>
     <row r="19">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1222.78</v>
+        <v>1205.28</v>
       </c>
     </row>
     <row r="20">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>58736.61</v>
+        <v>57482.4</v>
       </c>
     </row>
     <row r="21">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>36116.05</v>
+        <v>35281.5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/mar-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/mar-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/mar-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bienestar</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/mar-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/mar-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1062,7 +1082,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1123,7 +1147,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1184,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1245,7 +1277,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1306,7 +1342,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1367,7 +1407,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1428,7 +1472,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1554,7 +1602,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1615,7 +1667,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1676,7 +1732,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1737,7 +1797,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
